--- a/text/foundationScores/shapesphysical_6_seconds_MFT_MAC.xlsx
+++ b/text/foundationScores/shapesphysical_6_seconds_MFT_MAC.xlsx
@@ -425,166 +425,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG42"/>
+  <dimension ref="A1:AI42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>chunkEnd</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>chunkStart</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>V_neu</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>V_neg</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>V_pos</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>V_com</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sentence</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>full_text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_care_virtue</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_fairness_virtue</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_loyalty_virtue</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_authority_virtue</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_sanctity_virtue</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_care_vice</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_fairness_vice</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_loyalty_vice</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_authority_vice</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_sanctity_vice</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_moral_nonmoral</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_fairness_virtue</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_group_virtue</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_deference_virtue</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_heroism_virtue</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_reciprocity_virtue</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_family_virtue</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_property_virtue</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_fairness_vice</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_group_vice</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_deference_vice</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_heroism_vice</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_reciprocity_vice</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_family_vice</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_property_vice</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_moral_nonmoral</t>
         </is>
@@ -594,104 +604,114 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10.544</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.031</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>76</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>24</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>45.88</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Let's all go to the lobby.  Let's all go to the lobby.  Let's all go to the lobby to get ourselves a treat.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.07627118644067797</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>0.06818181818181818</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.0217391304347826</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>0.03525641025641026</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>0.1271186440677966</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.09274193548387097</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.08891752577319588</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.06683168316831684</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>0.07774390243902438</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>0.06428571428571428</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>0.08695652173913043</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.3491758241758242</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>0.05978260869565218</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>0.2523726273726274</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Z2" t="n">
         <v>0.1751644736842105</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AA2" t="n">
         <v>0.02142857142857143</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AB2" t="n">
         <v>0.19</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AC2" t="n">
         <v>0.1704545454545454</v>
       </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
         <v>0.1097560975609756</v>
       </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
       <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
         <v>0.05434782608695653</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AI2" t="n">
         <v>1.333333333333333</v>
       </c>
     </row>
@@ -699,104 +719,114 @@
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>19.616</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12.166</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>68.8</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>31.2</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>70.96000000000001</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">  Delicious things to eat.  The popcorn can't be beat.  The sparkling drinks are just dandy.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.07751937984496123</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>0.03846153846153847</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.07109799838019205</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.02729885057471264</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>0.1122073447654843</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.05061250805931657</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.01801801801801802</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>0.06346826586706646</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.13955463728191</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>0.6</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.06832298136645963</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0.06725146198830409</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.1</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>0.1470588235294118</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>0.1606263982102908</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>0.06521739130434782</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>0.1497524752475247</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AB3" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AC3" t="n">
         <v>0.08</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AD3" t="n">
         <v>0.07777777777777778</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AE3" t="n">
         <v>0.05921052631578947</v>
       </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
         <v>0.125</v>
       </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -804,34 +834,38 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26.224</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>19.996</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>93.2</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>6.800000000000001</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>2.58</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">  The chocolate bars and the candy.  So let's all go to the lobby to get ourselves</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
@@ -842,66 +876,72 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>0.1694915254237288</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.1236559139784946</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.1185567010309278</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>0.0891089108910891</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>0.1036585365853658</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>0.25</v>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
         <v>0.3367724867724868</v>
       </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
         <v>0.1233766233766234</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>0.07291666666666667</v>
       </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
         <v>0.2457142857142857</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AC4" t="n">
         <v>0.2088744588744589</v>
       </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
         <v>0.1044207317073171</v>
       </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
       <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
         <v>0.1725955204216074</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -909,104 +949,114 @@
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>49.077</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>30.811</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>84.7</v>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>15.3</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>40.19</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve"> To get ourselves a treat A small triangle overlapping a smaller circle slides into a rectangle.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.1525423728813559</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>0.1363636363636364</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.09580384226491405</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>0.07051282051282051</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>0.04770318021201414</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0.04104477611940299</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.05384615384615385</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
         <v>0.04028436018957346</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>0.1285714285714286</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>0.1739130434782609</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>0.1195652173913044</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>0.2160107334525939</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>0.131578947368421</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AA5" t="n">
         <v>0.04285714285714286</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AB5" t="n">
         <v>0.09854014598540146</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
         <v>0.04777070063694268</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AD5" t="n">
         <v>0.076</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AE5" t="n">
         <v>0.05038759689922481</v>
       </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
         <v>0.03365384615384615</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>0.055</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -1014,104 +1064,114 @@
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>61.657</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>49.758</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>100</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">  The triangle touches the circle which glides away.  The triangle slides to it and the circle moves away.  The triangle comes into contact with the circle again and the circle ricochets between the side of the rectangle and the triangle several times.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.02923279769680092</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>0.02386655687800983</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.01672594850948509</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>0.008287292817679559</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>0.04278738476876523</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.0876254674765824</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.06090027715867669</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>0.07380249548027622</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>0.04486529430690401</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>0.4615384615384616</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>0.01709401709401709</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.07965260048593381</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.05604133545310016</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>0.01422764227642277</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>0.08677905722385289</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>0.1340477950234048</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
         <v>0.03316730523627075</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AB6" t="n">
         <v>0.1355172324301879</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AC6" t="n">
         <v>0.07222222222222223</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AD6" t="n">
         <v>0.07950094638406327</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AE6" t="n">
         <v>0.1002838635454182</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AF6" t="n">
         <v>0.01282051282051282</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AG6" t="n">
         <v>0.021190428177724</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>0.08099452170248631</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>0.4615384615384616</v>
       </c>
     </row>
@@ -1119,104 +1179,114 @@
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>68.763</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>62.678</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>100</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">  The triangle moves in a ring around the circle, rotating.  A large triangle slides towards the rectangle.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.08000910746812386</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>0.0505050505050505</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.0740239986479635</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>0.06081081081081083</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.1217893528483283</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.05826763695168789</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>0.04464285714285714</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.07352941176470588</v>
       </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
       <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
         <v>0.1057971014492754</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>0.05172413793103448</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
         <v>0.1623931623931624</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AC7" t="n">
         <v>0.05514705882352941</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AD7" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AE7" t="n">
         <v>0.02459016393442623</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>0.07222222222222222</v>
       </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
         <v>0.05855855855855856</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>0.2857142857142857</v>
       </c>
     </row>
@@ -1224,104 +1294,114 @@
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>76.455</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>68.823</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>100</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve">  The small triangle slides outside the rectangle until it is adjacent to the large triangle.  After bouncing, both triangles slide out of the scene.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.0290696263949539</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>0.02525252525252525</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.02061855670103093</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.03294573643410853</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>0.05207739655761997</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.0486559403311848</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.05012019230769231</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>0.02103960396039604</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.04066255319247941</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>0.5</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>0.01930783242258652</v>
       </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
       <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
         <v>0.008333333333333333</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
         <v>0.04069767441860465</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
         <v>0.03623188405797102</v>
       </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
         <v>0.07277434649697423</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
         <v>0.1085075612718182</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AD8" t="n">
         <v>0.1055395526459356</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AE8" t="n">
         <v>0.09631240982859023</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AF8" t="n">
         <v>0.1092592592592593</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
         <v>0.03026778329197684</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>0.08704149192295743</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1329,104 +1409,114 @@
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>84.768</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>76.696</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>94</v>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>6</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>20.23</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">  The rectangle reassembles into a square-like structure with a triangular top and a line in the middle.  The triangles slide into the structure through a gap in the bottom.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.001629072681704261</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>0.04715322774178066</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.02397784206672032</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.001083032490974729</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>0.02163213463523061</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>0.04225591567363719</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>0.02393634402980198</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>0.05191053514131374</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>0.04007233574060454</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.04669992048001156</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>0.005767012687427913</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>0.03030053835948379</v>
       </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
         <v>0.006172839506172839</v>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>0.00329489291598023</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>0.0624124513618677</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Z9" t="n">
         <v>0.03767279090113736</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AA9" t="n">
         <v>0.01552001776889333</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AB9" t="n">
         <v>0.1171593760226901</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AC9" t="n">
         <v>0.0471976401179941</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AD9" t="n">
         <v>0.06931620500468352</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AE9" t="n">
         <v>0.06877874297393971</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AF9" t="n">
         <v>0.02222222222222222</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AG9" t="n">
         <v>0.0462962962962963</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AH9" t="n">
         <v>0.05426356589147287</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -1434,104 +1524,114 @@
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>92.56</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>85.709</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>91.8</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>8.200000000000001</v>
       </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>-15.31</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">  The triangles rotate 90 degrees.  The small triangle slides diagonally to the upper right, stopping at the middle line.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.03079847908745247</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>0.03387622149837134</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.05493242389794114</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.09310662849722583</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>0.04285714285714286</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>0.08381552021443725</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>0.07992413197917572</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>0.05525967513660945</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>0.02857460776677422</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>0.05959032545022218</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>0.07804101838755303</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>0.03846153846153846</v>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>0.04883720930232558</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>0.1257620521010081</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Z10" t="n">
         <v>0.02333333333333333</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>0.04151542649727767</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AB10" t="n">
         <v>0.1371396050097183</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AC10" t="n">
         <v>0.05928358040696691</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AD10" t="n">
         <v>0.08998715375351264</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AE10" t="n">
         <v>0.07677785568006718</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
         <v>0.01666666666666667</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AG10" t="n">
         <v>0.08884196297870331</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AH10" t="n">
         <v>0.06819767441860465</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AI10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1539,104 +1639,114 @@
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>102.871</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>93.839</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>85.2</v>
       </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
         <v>14.8</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>48.65</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">  The large triangle does the same.  The triangles rotate so their top corners touch and then the small triangle rotates so the top corner points up.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.02361111111111111</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>0.07155687307861221</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.02061855670103093</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.05500894454382827</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>0.03101503759398496</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>0.05737166480255235</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>0.02052238805970149</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>0.04826732673267327</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>0.03947207700200323</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>0.0272108843537415</v>
       </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
         <v>0.02325581395348837</v>
       </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
         <v>0.05426356589147287</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Z11" t="n">
         <v>0.08056724326009039</v>
       </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
         <v>0.09703246199596564</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AC11" t="n">
         <v>0.1026254450824916</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AD11" t="n">
         <v>0.101948717948718</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AE11" t="n">
         <v>0.07776295166687847</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="n">
         <v>0.066005291005291</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AG11" t="n">
         <v>0.02243589743589744</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AH11" t="n">
         <v>0.09475332475332476</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
         <v>0.375</v>
       </c>
     </row>
@@ -1644,104 +1754,114 @@
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>110.981</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>103.532</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>100</v>
       </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">  The large triangle slides diagonally down and rotates in place.  Both triangles move slightly, up and down, up and down.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.04722222222222222</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>0.0505050505050505</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.081906969861392</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>0.04130434782608695</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>0.05125</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>0.04606741573033708</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>0.04914529914529914</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.04207920792079208</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.03865979381443298</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
         <v>0.06511627906976744</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
       <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
         <v>0.08536585365853659</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Z12" t="n">
         <v>0.1208508648901356</v>
       </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
         <v>0.1129426129426129</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AC12" t="n">
         <v>0.05514705882352941</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AD12" t="n">
         <v>0.1460720130932897</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AE12" t="n">
         <v>0.06664623870078137</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AF12" t="n">
         <v>0.07222222222222222</v>
       </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
         <v>0.1198488811392037</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AI12" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -1749,104 +1869,114 @@
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>125.433</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>111.342</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>92.40000000000001</v>
       </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
         <v>7.6</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
         <v>20.23</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve">  The top of the structure rotates open and the small triangle moves slowly upwards while rotating.  The structure turns into a large V.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.04321816584634861</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>0.07773648434025793</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.06586023936204187</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>0.01744186046511628</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>0.01515151515151515</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>0.01590106007067138</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>0.03395186231007127</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>0.01794871794871795</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>0.07512903880023822</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>0.06459669745978554</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>0.04565217391304348</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
         <v>0.06570985832349469</v>
       </c>
-      <c r="U13" t="n">
+      <c r="W13" t="n">
         <v>0.07634803921568628</v>
       </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
         <v>0.04069767441860465</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Z13" t="n">
         <v>0.06988884198677361</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AA13" t="n">
         <v>0.05313479623824451</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AB13" t="n">
         <v>0.1304666541892819</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AC13" t="n">
         <v>0.05145887973023604</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AD13" t="n">
         <v>0.07646153846153847</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
         <v>0.07110232579497677</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
         <v>0.07558479532163742</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AG13" t="n">
         <v>0.01682692307692308</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AH13" t="n">
         <v>0.05677927927927928</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AI13" t="n">
         <v>0.4444444444444444</v>
       </c>
     </row>
@@ -1854,104 +1984,114 @@
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>145.036</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>125.533</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>100</v>
       </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve">  The branches of the V rotate up and down.  The V splits into two smaller Vs and the triangle moves left and right with the Vs. Again, the two Vs split in half, making four Vs. The four Vs move in the same direction as the triangle, which moves left and right.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.06116248679102387</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>0.06703740463588091</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.08439373678020441</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>0.06401776625325929</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>0.01052631578947368</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>0.0485724879495736</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>0.05418136340829608</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>0.03807526061530638</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>0.05548093162091042</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.06297766161484698</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>0.6428571428571429</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.1253543962859269</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>0.1118818681318681</v>
       </c>
-      <c r="U14" t="n">
+      <c r="W14" t="n">
         <v>0.1002262443438914</v>
       </c>
-      <c r="V14" t="n">
+      <c r="X14" t="n">
         <v>0.1313578861727505</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Y14" t="n">
         <v>0.04506437768240344</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Z14" t="n">
         <v>0.07727272727272727</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AA14" t="n">
         <v>0.07205467814804803</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AB14" t="n">
         <v>0.09463812050018947</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="n">
         <v>0.07946993029664451</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AD14" t="n">
         <v>0.06969987228607918</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0.08631629591894494</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AG14" t="n">
         <v>0.06854281767955801</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AH14" t="n">
         <v>0.05054525627044711</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AI14" t="n">
         <v>0.5333333333333333</v>
       </c>
     </row>
@@ -1959,104 +2099,114 @@
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>153.292</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>145.677</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>88.7</v>
       </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
         <v>11.3</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
         <v>31.82</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">  The Vs reform the original square-like structure.  The big triangle appears and the triangles move slightly up and down.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.04358030982201416</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>0.06039933883271934</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.04780994033519309</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>0.0604910939245342</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>0.04205819824822838</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>0.01219512195121951</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>0.0152027027027027</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>0.01452020202020202</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>0.008130081300813009</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.01587301587301587</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>1.2</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.09911749571021282</v>
       </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
         <v>0.08259808458608159</v>
       </c>
-      <c r="U15" t="n">
+      <c r="W15" t="n">
         <v>0.04324024382163917</v>
       </c>
-      <c r="V15" t="n">
+      <c r="X15" t="n">
         <v>0.02723806945388494</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Y15" t="n">
         <v>0.05997139385736916</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Z15" t="n">
         <v>0.03881280689196147</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AA15" t="n">
         <v>0.02866034931252322</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AB15" t="n">
         <v>0.03252032520325204</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AC15" t="n">
         <v>0.02607361963190184</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AD15" t="n">
         <v>0.02631578947368421</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AE15" t="n">
         <v>0.01984126984126984</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AF15" t="n">
         <v>0.02941176470588235</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AG15" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AH15" t="n">
         <v>0.02184873949579832</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AI15" t="n">
         <v>0.5714285714285714</v>
       </c>
     </row>
@@ -2064,104 +2214,114 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>161.902</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>154.634</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>100</v>
       </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve">  The big triangle moves diagonally up to the middle line.  Adjacent to the little triangle, it moves up and down once.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.03899740340270511</v>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>0.03696903460837887</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.0216848572595315</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>0.01151761517615176</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>0.04432493215187557</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>0.09748780645112742</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>0.04262121335199195</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>0.076952269757336</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.04217672755504284</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>1.5</v>
       </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
         <v>0.06512258368694013</v>
       </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
         <v>0.06193950448396413</v>
       </c>
-      <c r="V16" t="n">
+      <c r="X16" t="n">
         <v>0.02179691653375864</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Y16" t="n">
         <v>0.07044645462503647</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Z16" t="n">
         <v>0.06768208399787347</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AA16" t="n">
         <v>0.05732390215148836</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AB16" t="n">
         <v>0.1880048995448091</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AC16" t="n">
         <v>0.04098123314693161</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AD16" t="n">
         <v>0.0554914358356751</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AE16" t="n">
         <v>0.03438937148696986</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AF16" t="n">
         <v>0.01111111111111111</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AG16" t="n">
         <v>0.02314814814814815</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AH16" t="n">
         <v>0.03679361869452871</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AI16" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -2169,104 +2329,114 @@
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>172.334</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>165.827</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>100</v>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">  The large triangle moves diagonally down.  The small triangle does the same.  The small triangle slides down out of the structure.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.03200364298724954</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>0.04353535353535353</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.04251282526563701</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.04186046511627907</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>0.03816254416961131</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>0.05716014521984673</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>0.04307692307692308</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>0.05847183870030694</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.07458216197995296</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
         <v>0.02232142857142857</v>
       </c>
-      <c r="U17" t="n">
+      <c r="W17" t="n">
         <v>0.03676470588235294</v>
       </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
         <v>0.08139534883720931</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Z17" t="n">
         <v>0.05289855072463769</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AA17" t="n">
         <v>0.02586206896551724</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AB17" t="n">
         <v>0.1797367271819827</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AC17" t="n">
         <v>0.07534423004870738</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AD17" t="n">
         <v>0.1144615384615385</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AE17" t="n">
         <v>0.06268267886643793</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AF17" t="n">
         <v>0.03611111111111111</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AG17" t="n">
         <v>0.03365384615384615</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AH17" t="n">
         <v>0.08427927927927928</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AI17" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -2274,104 +2444,114 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>184.531</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>173.655</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
         <v>12.4</v>
       </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
         <v>-34</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve">  The large triangle disappears and the entire structure rotates 360 degrees.  The large triangle appears at the bottom.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>0.03777777777777778</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>0.07464646464646466</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.06084618755613848</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>0.02037037037037037</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>0.004597701149425288</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>0.04023414634146342</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>0.02439024390243903</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>0.016</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>0.06956325474728248</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.06706947119318253</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>1</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.0423728813559322</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>0.04090909090909091</v>
       </c>
-      <c r="U18" t="n">
+      <c r="W18" t="n">
         <v>0.01923076923076923</v>
       </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Z18" t="n">
         <v>0.1372410960511647</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AA18" t="n">
         <v>0.03977272727272727</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AB18" t="n">
         <v>0.1084839568446126</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AC18" t="n">
         <v>0.09288290788013319</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AD18" t="n">
         <v>0.1146589259796807</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AE18" t="n">
         <v>0.06824095758521988</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AF18" t="n">
         <v>0.1204678362573099</v>
       </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
         <v>0.0657014157014157</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AI18" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -2379,104 +2559,114 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>192.599</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>184.651</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>100</v>
       </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve"> The small triangle moves into the structure, moves up and down next to the large triangle once, and then slides diagonally up to the middle of the structure.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.03222742648972157</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>0.04776334776334776</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.04895057512174948</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.01495016611295681</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.01845166209794738</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>0.05097161813579725</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>0.02346134430940084</v>
       </c>
-      <c r="P19" t="n">
+      <c r="R19" t="n">
         <v>0.07483082644499621</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
         <v>0.06660067686118527</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>1.75</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
         <v>0.04957567185289958</v>
       </c>
-      <c r="U19" t="n">
+      <c r="W19" t="n">
         <v>0.05882352941176471</v>
       </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
         <v>0.03255813953488372</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Z19" t="n">
         <v>0.07431884057971014</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AA19" t="n">
         <v>0.04827586206896552</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AB19" t="n">
         <v>0.1893621209615824</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AC19" t="n">
         <v>0.04116710378418884</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AD19" t="n">
         <v>0.06871640058055153</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AE19" t="n">
         <v>0.03630689380714462</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AF19" t="n">
         <v>0.04222222222222222</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AG19" t="n">
         <v>0.01346153846153846</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AH19" t="n">
         <v>0.04542342342342343</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AI19" t="n">
         <v>0.8333333333333334</v>
       </c>
     </row>
@@ -2484,104 +2674,114 @@
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>202.69</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>192.88</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>91.3</v>
       </c>
-      <c r="C20" t="n">
+      <c r="E20" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>-29.6</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve">  Both triangles rotate 90 degrees and then bounce slowly in place.  The structure's lower pieces form four Vs that again move up and down.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>0.03888888888888889</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.04861861398363945</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.06489255372313843</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>0.03416666666666666</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>0.06851229777211476</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>0.08689458689458689</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>0.03828828828828829</v>
       </c>
-      <c r="P20" t="n">
+      <c r="R20" t="n">
         <v>0.01626016260162602</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="S20" t="n">
         <v>0.06507936507936508</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>0.375</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
         <v>0.07566891722930733</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
       <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
         <v>0.05691056910569106</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Z20" t="n">
         <v>0.03225806451612903</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AA20" t="n">
         <v>0.0303030303030303</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AB20" t="n">
         <v>0.108058608058608</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AC20" t="n">
         <v>0.01754385964912281</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
         <v>0.1052120758816275</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AE20" t="n">
         <v>0.05556714508233199</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AF20" t="n">
         <v>0.06822742474916388</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AG20" t="n">
         <v>0.1037851037851038</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AH20" t="n">
         <v>0.04086021505376344</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AI20" t="n">
         <v>0.375</v>
       </c>
     </row>
@@ -2589,104 +2789,114 @@
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>216.17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>202.89</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>93.60000000000001</v>
       </c>
-      <c r="C21" t="n">
+      <c r="E21" t="n">
         <v>6.4</v>
       </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
         <v>-12.8</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve">  The small triangle moves upward.  The Vs are positioned around the triangle moving with it.  The Vs become rigid and form separate bars.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.04290198814091385</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>0.016</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.03175882189497083</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.05573340619256126</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>0.02040816326530612</v>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>0.06516593977508861</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>0.0940000880299388</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>0.05513090353798318</v>
       </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
         <v>0.06142951251646904</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="S21" t="n">
         <v>0.05658846027809976</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>0.625</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>0.03571428571428571</v>
       </c>
-      <c r="T21" t="n">
+      <c r="V21" t="n">
         <v>0.04053379416282642</v>
       </c>
-      <c r="U21" t="n">
+      <c r="W21" t="n">
         <v>0.0677196804647785</v>
       </c>
-      <c r="V21" t="n">
+      <c r="X21" t="n">
         <v>0.007575757575757576</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Y21" t="n">
         <v>0.04565030146425495</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Z21" t="n">
         <v>0.01111111111111111</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AA21" t="n">
         <v>0.05678313836429901</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AB21" t="n">
         <v>0.1613674413068202</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AC21" t="n">
         <v>0.08378070973612374</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AD21" t="n">
         <v>0.08129265555281816</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AE21" t="n">
         <v>0.05203283778042444</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AF21" t="n">
         <v>0.05349531116794545</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AG21" t="n">
         <v>0.07332974996018474</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AH21" t="n">
         <v>0.08982954545454545</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AI21" t="n">
         <v>0.8571428571428571</v>
       </c>
     </row>
@@ -2694,104 +2904,114 @@
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>229.665</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>216.37</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>100</v>
       </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Other pieces form four longer lines.  The long line on the left has hinges and moves towards the triangle.  The triangle moves to the upper right while the lines move down.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.03038899364208689</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>0.04586441891503756</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.05943904595192275</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.02542009452126729</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>0.002808988764044944</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>0.06217877482090099</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>0.06399804520623968</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>0.03630140726435787</v>
       </c>
-      <c r="P22" t="n">
+      <c r="R22" t="n">
         <v>0.08245782805927376</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>0.06354875529538334</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>2</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>0.06451775625504438</v>
       </c>
-      <c r="T22" t="n">
+      <c r="V22" t="n">
         <v>0.05663955360612959</v>
       </c>
-      <c r="U22" t="n">
+      <c r="W22" t="n">
         <v>0.04479638009049774</v>
       </c>
-      <c r="V22" t="n">
+      <c r="X22" t="n">
         <v>0.05882266600234308</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Y22" t="n">
         <v>0.05348883832128352</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Z22" t="n">
         <v>0.07208944024012517</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AA22" t="n">
         <v>0.0735344854902312</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AB22" t="n">
         <v>0.1184548031630207</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AC22" t="n">
         <v>0.09206592841484981</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AD22" t="n">
         <v>0.1416484554719466</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AE22" t="n">
         <v>0.03157347251624206</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AF22" t="n">
         <v>0.07640128611191092</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AG22" t="n">
         <v>0.05737744453214066</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AH22" t="n">
         <v>0.03626233861612951</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2799,104 +3019,114 @@
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>237.955</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>229.766</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>100</v>
       </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve">  The lines then move vertically, extending towards the triangle.  The moving lines reform the square-like structure and the small triangle moves down to the middle line.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.02772645092451259</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>0.04456369362372194</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.05085998711369523</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.02792909506569</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>0.01730100947261496</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>0.0395912582852509</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>0.03473292380392394</v>
       </c>
-      <c r="O23" t="n">
+      <c r="Q23" t="n">
         <v>0.02762983756830473</v>
       </c>
-      <c r="P23" t="n">
+      <c r="R23" t="n">
         <v>0.05014497563434457</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>0.04011313764643056</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>2</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>0.05762723600930991</v>
       </c>
-      <c r="T23" t="n">
+      <c r="V23" t="n">
         <v>0.0361498466318607</v>
       </c>
-      <c r="U23" t="n">
+      <c r="W23" t="n">
         <v>0.01839748244977003</v>
       </c>
-      <c r="V23" t="n">
+      <c r="X23" t="n">
         <v>0.0306243271646896</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Y23" t="n">
         <v>0.05123768476345921</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Z23" t="n">
         <v>0.04218722659667542</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AA23" t="n">
         <v>0.05514997695370923</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AB23" t="n">
         <v>0.1016578745718986</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
         <v>0.09577380595562852</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
         <v>0.1460484132993011</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AE23" t="n">
         <v>0.04670210776556444</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AF23" t="n">
         <v>0.05912664582741309</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AG23" t="n">
         <v>0.03301174134507468</v>
       </c>
-      <c r="AF23" t="n">
+      <c r="AH23" t="n">
         <v>0.03684602523179815</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -2904,104 +3134,114 @@
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>252.428</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>242.609</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>100</v>
       </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve">  The large triangle appears, moves left and then rotates to point diagonally up.  It bounces.  The little triangle rotates 90 degrees and slides diagonally down.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.02666970248937462</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>0.02592592592592592</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.06207967820837887</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>0.02781541704305932</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>0.003831417624521073</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>0.05881951268222835</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>0.06951843885501301</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>0.01868802440884821</v>
       </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
         <v>0.06668417148082677</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>0.0563116647059269</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.05331124421222547</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>0.06596320346320346</v>
       </c>
-      <c r="U24" t="n">
+      <c r="W24" t="n">
         <v>0.05399698340874812</v>
       </c>
-      <c r="V24" t="n">
+      <c r="X24" t="n">
         <v>0.03929675568964875</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Y24" t="n">
         <v>0.03864144803742119</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Z24" t="n">
         <v>0.1079663916048355</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AA24" t="n">
         <v>0.02933815350389321</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AB24" t="n">
         <v>0.1095835138111945</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AC24" t="n">
         <v>0.07431724367985715</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AD24" t="n">
         <v>0.07750884173297967</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AE24" t="n">
         <v>0.04797290710536032</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AF24" t="n">
         <v>0.0622308069659063</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AG24" t="n">
         <v>0.01992753623188406</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AH24" t="n">
         <v>0.05811628802003843</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AI24" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -3009,104 +3249,114 @@
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>260.844</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>252.768</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>88.2</v>
       </c>
-      <c r="C25" t="n">
+      <c r="E25" t="n">
         <v>11.8</v>
       </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
         <v>-34</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t xml:space="preserve">  Both bounce and the little triangle exits the structure.  The large triangle disappears and the structure rotates 360 degrees.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.02361111111111111</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>0.08358585858585858</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.07554328788382662</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.01626016260162602</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
         <v>0.0223342939481268</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>0.02671232876712329</v>
       </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
         <v>0.04542984786283506</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>0.08817535962060373</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
         <v>0.03508771929824561</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Y25" t="n">
         <v>0.07046979865771812</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Z25" t="n">
         <v>0.147025171624714</v>
       </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
         <v>0.1394743004332045</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AC25" t="n">
         <v>0.05514705882352941</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AD25" t="n">
         <v>0.1394230769230769</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AE25" t="n">
         <v>0.02459016393442623</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AF25" t="n">
         <v>0.07222222222222222</v>
       </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
         <v>0.08754406580493537</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>0.2222222222222222</v>
       </c>
     </row>
@@ -3114,104 +3364,114 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>273.611</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>261.084</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>100</v>
       </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t xml:space="preserve">  The large triangle appears.  The small triangle slides into the structure, bounces adjacent to the large triangle and glides diagonally upwards towards the middle line.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.02698412698412698</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>0.05331890331890331</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.04346156254009891</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.02950043066322136</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>0.003284072249589491</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>0.04931278703572737</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>0.03224394520251683</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.03947119652614961</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>0.05142433690313107</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>0.06002418903983615</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>0.02824858757062147</v>
       </c>
-      <c r="T26" t="n">
+      <c r="V26" t="n">
         <v>0.03882388238823883</v>
       </c>
-      <c r="U26" t="n">
+      <c r="W26" t="n">
         <v>0.01282051282051282</v>
       </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
         <v>0.06894996476391825</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Z26" t="n">
         <v>0.08140859394863971</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AA26" t="n">
         <v>0.005747126436781609</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AB26" t="n">
         <v>0.1227654346788435</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AC26" t="n">
         <v>0.07628709282033087</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
         <v>0.1112734871177264</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AE26" t="n">
         <v>0.08080619297050884</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AF26" t="n">
         <v>0.05925925925925925</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AG26" t="n">
         <v>0.03436609686609687</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AH26" t="n">
         <v>0.08926606008001359</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AI26" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -3219,104 +3479,114 @@
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>286.15</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>275.694</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>94.3</v>
       </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
         <v>5.7</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>20.23</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t xml:space="preserve">  It rotates until it points up, as does the large triangle below.  Both bob slightly up and down.  The top of the square-like structure opens and the small triangle moves upwards.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.02829877517107888</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>0.04846892090529991</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.03789982011066514</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.01852489295609101</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>0.01392905340273761</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>0.02766576595302432</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>0.03395186231007127</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.02703962703962704</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>0.06687834743177393</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>0.04872368158676965</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>0.75</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>0.01978673822470164</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
         <v>0.02217607973421927</v>
       </c>
-      <c r="U27" t="n">
+      <c r="W27" t="n">
         <v>0.04706895678167908</v>
       </c>
-      <c r="V27" t="n">
+      <c r="X27" t="n">
         <v>0.001976935749588138</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Y27" t="n">
         <v>0.03800561035200435</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Z27" t="n">
         <v>0.06561068716340332</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AA27" t="n">
         <v>0.02310511410961186</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AB27" t="n">
         <v>0.1043733233514255</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AC27" t="n">
         <v>0.06157526704949497</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
         <v>0.06116923076923077</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AE27" t="n">
         <v>0.04665777100012708</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AF27" t="n">
         <v>0.0396031746031746</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
         <v>0.01346153846153846</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>0.05685199485199485</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>0.5555555555555556</v>
       </c>
     </row>
@@ -3324,104 +3594,114 @@
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>297.106</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>288.678</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>100</v>
       </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t xml:space="preserve">  The square forms six lines.  Two have moving parts.  The lines move sideways all together, and a long line with hinges swings out towards the triangle.</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>0.02127659574468085</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>0.05874587480236584</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.06402016677518864</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>0.008849557522123892</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>0.01457725947521866</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>0.07891248928283211</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>0.02237056816496069</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.0211118930330753</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>0.07066389905006969</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>0.06163385639168906</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>1.4</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>0.04166666666666667</v>
       </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
       <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
         <v>0.03246753246753246</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Y28" t="n">
         <v>0.06653456908490465</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Z28" t="n">
         <v>0.06708414872798434</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AA28" t="n">
         <v>0.08698974776277039</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AB28" t="n">
         <v>0.1085802804916608</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AC28" t="n">
         <v>0.1895621012701799</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AD28" t="n">
         <v>0.2083564555669624</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AE28" t="n">
         <v>0.09313846362274357</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>0.09022392220623612</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AG28" t="n">
         <v>0.03698412698412699</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AH28" t="n">
         <v>0.03803413907664108</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AI28" t="n">
         <v>1.4</v>
       </c>
     </row>
@@ -3429,104 +3709,114 @@
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>304.493</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>297.666</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>100</v>
       </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve">  The triangle moves downwards.  A small square appears from the left.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.01639344262295082</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>0.01363636363636363</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.03508503140799754</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>0.05162575366063737</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>0.00574712643678161</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>0.076627031653526</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>0.08147642189403459</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.05495511353634923</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>0.06241604807352422</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>0.05202587374318626</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0.0423728813559322</v>
       </c>
-      <c r="T29" t="n">
+      <c r="V29" t="n">
         <v>0.06323051948051948</v>
       </c>
-      <c r="U29" t="n">
+      <c r="W29" t="n">
         <v>0.05599547511312217</v>
       </c>
-      <c r="V29" t="n">
+      <c r="X29" t="n">
         <v>0.04140127388535032</v>
       </c>
-      <c r="W29" t="n">
+      <c r="Y29" t="n">
         <v>0.06342494714587738</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Z29" t="n">
         <v>0.08843700159489633</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AA29" t="n">
         <v>0.02586206896551724</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AB29" t="n">
         <v>0.1439081934928902</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AC29" t="n">
         <v>0.07916173222801909</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AD29" t="n">
         <v>0.08455172413793104</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AE29" t="n">
         <v>0.04503506829088225</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AF29" t="n">
         <v>0.03973509933774835</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AG29" t="n">
         <v>0.01682692307692308</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>0.07090239912758997</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AI29" t="n">
         <v>1.333333333333333</v>
       </c>
     </row>
@@ -3534,104 +3824,114 @@
       <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>312.08</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>305.634</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>100</v>
       </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t xml:space="preserve">  Two of the lines rotate to point at them.  The square and the triangle move counterclockwise around the screen.</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>0.07301587301587302</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.1279277916446058</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.01754385964912281</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>0.0381416789218848</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>0.0221483942414175</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
         <v>0.04715679689136385</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>0.0321009122400254</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>0.75</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.1481046365914787</v>
       </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
         <v>0.05</v>
       </c>
-      <c r="V30" t="n">
+      <c r="X30" t="n">
         <v>0.05681818181818182</v>
       </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
         <v>0.05</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AA30" t="n">
         <v>0.08629032258064517</v>
       </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
         <v>0.1592927247234772</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AD30" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AE30" t="n">
         <v>0.07964601769911504</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AF30" t="n">
         <v>0.1219565217391304</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AG30" t="n">
         <v>0.05978260869565218</v>
       </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -3639,104 +3939,114 @@
       <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>320.793</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>312.8</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>100</v>
       </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t xml:space="preserve">  The square and triangle move up and down.  The square leaves and re-enters with a small circle.  The circle is between the triangle and square.</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>0.06319514661274014</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>0.09487299153276886</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>0.1077114427860696</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>0.1163461538461538</v>
       </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
         <v>0.07289305584174738</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>0.25</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>0.1388888888888889</v>
       </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
       <c r="V31" t="n">
         <v>0</v>
       </c>
       <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
         <v>0.1950317124735729</v>
       </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
       <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
         <v>0.09854014598540146</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AC31" t="n">
         <v>0.2422151450813871</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AD31" t="n">
         <v>0.1593333333333333</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AE31" t="n">
         <v>0.1273106738223017</v>
       </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
         <v>0.06698717948717949</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AH31" t="n">
         <v>0.055</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AI31" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -3744,104 +4054,114 @@
       <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>333.838</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>320.873</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>90.90000000000001</v>
       </c>
-      <c r="C32" t="n">
+      <c r="E32" t="n">
         <v>9.1</v>
       </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
         <v>-49.39</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t xml:space="preserve">  The circle moves quickly towards the lines.  When the circle touches the lines, they collapse into pieces.  The triangle moves above the pieces, making a small loop and then glides off the screen.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.02376735129702908</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>0.04786447376808823</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>0.083622597801061</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.02918938094278378</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>0.01846282372598162</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>0.06184794445184405</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>0.05269744317154326</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>0.01837606837606838</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>0.07481716117713907</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>0.06125364223497812</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>1.125</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>0.08506222740357819</v>
       </c>
-      <c r="T32" t="n">
+      <c r="V32" t="n">
         <v>0.04965507329692441</v>
       </c>
-      <c r="U32" t="n">
+      <c r="W32" t="n">
         <v>0.08872882486327864</v>
       </c>
-      <c r="V32" t="n">
+      <c r="X32" t="n">
         <v>0.09505637397428443</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Y32" t="n">
         <v>0.05355884425651868</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Z32" t="n">
         <v>0.06493506493506494</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AA32" t="n">
         <v>0.07332564720679176</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AB32" t="n">
         <v>0.09408839335846635</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AC32" t="n">
         <v>0.09960757909668315</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AD32" t="n">
         <v>0.1256103896103896</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AE32" t="n">
         <v>0.01439645625692137</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AF32" t="n">
         <v>0.08387747518182301</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AG32" t="n">
         <v>0.01556776556776557</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AH32" t="n">
         <v>0.055</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AI32" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -3849,104 +4169,114 @@
       <c r="A33" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>348.294</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>339.623</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>94.19999999999999</v>
       </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
         <v>5.800000000000001</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>20.23</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t xml:space="preserve">  The pieces are stationary.  The triangle reappears from the bottom left of the screen.  The top of the triangle touches one of the pieces which rotates up and back down.</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.02631578947368421</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>0.03571428571428571</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>0.06896551724137931</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>0.06109725685785537</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>0.05606407322654462</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>0.0451219512195122</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>0.04415954415954416</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>0.25</v>
       </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
       <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
         <v>0.1656050955414013</v>
       </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
         <v>0.1477832512315271</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AC33" t="n">
         <v>0.221105527638191</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AD33" t="n">
         <v>0.1862068965517241</v>
       </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
         <v>0.1589403973509934</v>
       </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
         <v>0.1450381679389313</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AI33" t="n">
         <v>0.1111111111111111</v>
       </c>
     </row>
@@ -3954,67 +4284,71 @@
       <c r="A34" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>357.706</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>348.735</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>100</v>
       </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t xml:space="preserve">  The motion is repeated on another piece and the triangle touches the circle underneath it.  The circle and triangle moving in sync move up and make a full revolution.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.05360798875953432</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>0.05930628803245437</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>0.02531073446327683</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.01238938053097345</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>0.043937575030012</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>0.04973075704783022</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>0.04823920265780732</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>0.06015037593984962</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>0.07499497234791354</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
       <c r="U34" t="n">
         <v>0</v>
       </c>
@@ -4022,36 +4356,42 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
         <v>0.1709401709401709</v>
       </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
         <v>0.07317073170731707</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AB34" t="n">
         <v>0.1266201395812562</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AC34" t="n">
         <v>0.2333333333333333</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AD34" t="n">
         <v>0.1973392461197339</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AE34" t="n">
         <v>0.1518418688230009</v>
       </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="AF34" t="n">
+      <c r="AH34" t="n">
         <v>0.09090909090909091</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AI34" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -4059,104 +4399,114 @@
       <c r="A35" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>366.137</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>357.826</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>100</v>
       </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t xml:space="preserve">  The triangle moves off screen while the circle and the pieces are stationary.  The pieces reform the square-like structure.</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.02566566780647199</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>0.07122262534268195</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.0864947098495837</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.0330648928317407</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>0.02847956996563808</v>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
         <v>0.02432432432432433</v>
       </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
         <v>0.0416401555319901</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
         <v>0.02689075630252101</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>0.07565948580570749</v>
       </c>
-      <c r="T35" t="n">
+      <c r="V35" t="n">
         <v>0.08534722966455899</v>
       </c>
-      <c r="U35" t="n">
+      <c r="W35" t="n">
         <v>0.05519244734931009</v>
       </c>
-      <c r="V35" t="n">
+      <c r="X35" t="n">
         <v>0.01611540573649305</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Y35" t="n">
         <v>0.009079118028534372</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Z35" t="n">
         <v>0.02878390201224847</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AA35" t="n">
         <v>0.03850852351601976</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AB35" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
         <v>0.03508771929824561</v>
       </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
         <v>0.0392156862745098</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AG35" t="n">
         <v>0.0303030303030303</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="AH35" t="n">
         <v>0.0196078431372549</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AI35" t="n">
         <v>0.375</v>
       </c>
     </row>
@@ -4164,104 +4514,114 @@
       <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>380.496</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>369.762</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>92.10000000000001</v>
       </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
         <v>7.9</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>20.23</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t xml:space="preserve">  The small triangle moves slowly into it from the top.  The large triangle appears in the bottom, moves left, and bounces once.</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.0375986642380085</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>0.02592592592592592</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.04806468715465286</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.03441716910709158</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>0.003831417624521073</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>0.05108468776901733</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>0.07458788486629334</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>0.03663674235756615</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>0.08220714966512559</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>0.05410646147935347</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>1.5</v>
       </c>
-      <c r="S36" t="n">
+      <c r="U36" t="n">
         <v>0.02824858757062147</v>
       </c>
-      <c r="T36" t="n">
+      <c r="V36" t="n">
         <v>0.05703463203463204</v>
       </c>
-      <c r="U36" t="n">
+      <c r="W36" t="n">
         <v>0.06184012066365008</v>
       </c>
-      <c r="V36" t="n">
+      <c r="X36" t="n">
         <v>0.02760084925690021</v>
       </c>
-      <c r="W36" t="n">
+      <c r="Y36" t="n">
         <v>0.04228329809725159</v>
       </c>
-      <c r="X36" t="n">
+      <c r="Z36" t="n">
         <v>0.09422370154635601</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="AA36" t="n">
         <v>0.03448275862068965</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AB36" t="n">
         <v>0.150069849792981</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AC36" t="n">
         <v>0.07115684109318919</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AD36" t="n">
         <v>0.08200884173297968</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AE36" t="n">
         <v>0.03822010017206357</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AF36" t="n">
         <v>0.05056414029923963</v>
       </c>
-      <c r="AE36" t="n">
+      <c r="AG36" t="n">
         <v>0.01121794871794872</v>
       </c>
-      <c r="AF36" t="n">
+      <c r="AH36" t="n">
         <v>0.0667877856045795</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AI36" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -4269,67 +4629,71 @@
       <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>388.967</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>381.717</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>100</v>
       </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t xml:space="preserve"> The small triangle rotates 90 degrees, glides diagonally down, and bounces next to the large triangle.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.04722222222222222</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>0.0505050505050505</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.04123711340206185</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.05232558139534884</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
         <v>0.04770318021201414</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>0.04104477611940299</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>0.05384615384615385</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>0.04207920792079208</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>0.07894415400400645</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
@@ -4337,36 +4701,42 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
         <v>0.08139534883720931</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Z37" t="n">
         <v>0.07246376811594203</v>
       </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
         <v>0.1455486929939485</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AC37" t="n">
         <v>0.1029177594604721</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AD37" t="n">
         <v>0.1529230769230769</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AE37" t="n">
         <v>0.07497776083365104</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AF37" t="n">
         <v>0.07222222222222222</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="AG37" t="n">
         <v>0.03365384615384615</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AH37" t="n">
         <v>0.1135585585585586</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AI37" t="n">
         <v>0.2857142857142857</v>
       </c>
     </row>
@@ -4374,104 +4744,114 @@
       <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>395.836</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>388.987</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>100</v>
       </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t xml:space="preserve">  It slides out of the structure.  The structure reconfigures into a rectangle with a gap in the upper left side and a circle in the bottom left.</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>0.05500000000000001</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>0.02580645161290323</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>0.02352941176470588</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>0.07055702917771883</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>0.04887780548628429</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>0.07342268715266426</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>0.05560975609756098</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
         <v>0.07342287342287342</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
       <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
         <v>0.1656050955414013</v>
       </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
         <v>0.1477832512315271</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AC38" t="n">
         <v>0.221105527638191</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AD38" t="n">
         <v>0.1862068965517241</v>
       </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
         <v>0.1589403973509934</v>
       </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
         <v>0.1450381679389313</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AI38" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -4479,104 +4859,114 @@
       <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>405.689</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>396.416</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>100</v>
       </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t xml:space="preserve">  The small triangle slides through the gap.  It touches the angled bar which rotates to close the gap.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>0.03848133848133849</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>0.03405797101449275</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.01132075471698113</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.04950166112956811</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>0.0910501362707245</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>0.04985050285403643</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>0.02269242025168276</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>0.1017582417582417</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>0.01544401544401544</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>0.01611374407582938</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>1</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.07815126050420168</v>
       </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
       <c r="V39" t="n">
         <v>0</v>
       </c>
       <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
         <v>0.1018826135105205</v>
       </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AB39" t="n">
         <v>0.06569343065693431</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AC39" t="n">
         <v>0.118094220005048</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AD39" t="n">
         <v>0.1778380858734841</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AE39" t="n">
         <v>0.05424069881777229</v>
       </c>
-      <c r="AD39" t="n">
+      <c r="AF39" t="n">
         <v>0.0529595015576324</v>
       </c>
-      <c r="AE39" t="n">
+      <c r="AG39" t="n">
         <v>0.0954878454878455</v>
       </c>
-      <c r="AF39" t="n">
+      <c r="AH39" t="n">
         <v>0.1057723577235772</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AI39" t="n">
         <v>0.4285714285714285</v>
       </c>
     </row>
@@ -4584,34 +4974,38 @@
       <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>415.718</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>406.61</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>100</v>
       </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t xml:space="preserve"> The triangle slides towards the circle until they are touching.</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
@@ -4682,6 +5076,12 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4689,33 +5089,37 @@
       <c r="A41" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>424.345</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>416.379</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>90.90000000000001</v>
       </c>
-      <c r="C41" t="n">
+      <c r="E41" t="n">
         <v>9.1</v>
       </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
         <v>-15.31</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t xml:space="preserve">  The circle moves upward and stops.  The triangle moves towards the circle and the circle moves away.</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
-      </c>
-      <c r="H41" t="n">
-        <v>0.04918032786885245</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0.04918032786885245</v>
@@ -4724,69 +5128,75 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>0.04918032786885245</v>
       </c>
       <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
         <v>0.02093908629441624</v>
       </c>
-      <c r="N41" t="n">
+      <c r="P41" t="n">
         <v>0.1121659368866073</v>
       </c>
-      <c r="O41" t="n">
+      <c r="Q41" t="n">
         <v>0.03005115089514066</v>
       </c>
-      <c r="P41" t="n">
+      <c r="R41" t="n">
         <v>0.1470652173913043</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="S41" t="n">
         <v>0.04938217890706578</v>
       </c>
-      <c r="R41" t="n">
+      <c r="T41" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
         <v>0.06696428571428571</v>
       </c>
-      <c r="U41" t="n">
+      <c r="W41" t="n">
         <v>0.1102941176470588</v>
       </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="X41" t="n">
+      <c r="Z41" t="n">
         <v>0.09674796747967479</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AA41" t="n">
         <v>0.07758620689655173</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AB41" t="n">
         <v>0.2218934911242604</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AC41" t="n">
         <v>0.05416666666666667</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AD41" t="n">
         <v>0.03741496598639456</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AE41" t="n">
         <v>0.05102040816326531</v>
       </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0</v>
-      </c>
       <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
         <v>0.04646017699115045</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AI41" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -4794,104 +5204,114 @@
       <c r="A42" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>432.152</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>424.686</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>93.5</v>
       </c>
-      <c r="C42" t="n">
+      <c r="E42" t="n">
         <v>6.5</v>
       </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
         <v>-15.31</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t xml:space="preserve">  A square appears on the left and moves towards the rectangle.  The square stops.  It touches the bar which rotates to make a gap.</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H42" t="n">
+      <c r="J42" t="n">
         <v>0.03692427790788446</v>
       </c>
-      <c r="I42" t="n">
+      <c r="K42" t="n">
         <v>0.03663372859025032</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>0.03938877984337916</v>
       </c>
-      <c r="K42" t="n">
+      <c r="M42" t="n">
         <v>0.04894179894179894</v>
       </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
         <v>0.0551541399411582</v>
       </c>
-      <c r="M42" t="n">
+      <c r="O42" t="n">
         <v>0.05760496862263052</v>
       </c>
-      <c r="N42" t="n">
+      <c r="P42" t="n">
         <v>0.04876322706746648</v>
       </c>
-      <c r="O42" t="n">
+      <c r="Q42" t="n">
         <v>0.05099705786204641</v>
       </c>
-      <c r="P42" t="n">
+      <c r="R42" t="n">
         <v>0.04993283845881937</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="S42" t="n">
         <v>0.02550695491871963</v>
       </c>
-      <c r="R42" t="n">
+      <c r="T42" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="S42" t="n">
+      <c r="U42" t="n">
         <v>0.0673728813559322</v>
       </c>
-      <c r="T42" t="n">
+      <c r="V42" t="n">
         <v>0.06323051948051948</v>
       </c>
-      <c r="U42" t="n">
+      <c r="W42" t="n">
         <v>0.05599547511312217</v>
       </c>
-      <c r="V42" t="n">
+      <c r="X42" t="n">
         <v>0.04140127388535032</v>
       </c>
-      <c r="W42" t="n">
+      <c r="Y42" t="n">
         <v>0.05844155844155844</v>
       </c>
-      <c r="X42" t="n">
+      <c r="Z42" t="n">
         <v>0.08843700159489633</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AA42" t="n">
         <v>0.05363984674329501</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AB42" t="n">
         <v>0.09463812050018947</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AC42" t="n">
         <v>0.07450715114031697</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AD42" t="n">
         <v>0.1021072796934866</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AE42" t="n">
         <v>0.01984126984126984</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AF42" t="n">
         <v>0.03973509933774835</v>
       </c>
-      <c r="AE42" t="n">
+      <c r="AG42" t="n">
         <v>0.01785714285714286</v>
       </c>
-      <c r="AF42" t="n">
+      <c r="AH42" t="n">
         <v>0.04340239912758997</v>
       </c>
-      <c r="AG42" t="n">
+      <c r="AI42" t="n">
         <v>0.5714285714285714</v>
       </c>
     </row>
